--- a/public/file/Dudi.xlsx
+++ b/public/file/Dudi.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nginx\html\listrik\public\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nginx\html\listriksmkbkt.my.id\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2CAE9D-0C4D-4681-B6A2-AEABD11AAD42}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C903D67-D9FC-41DF-BCAF-181590CBCE68}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{0924806D-2D3F-478E-8271-B5933865398C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="96">
   <si>
     <t>nama_perusahaan</t>
   </si>
@@ -45,9 +45,6 @@
     <t>kuota</t>
   </si>
   <si>
-    <t>PT. SATRIA TEKNIK MANDIRI</t>
-  </si>
-  <si>
     <t>Koto Hilalang Baso</t>
   </si>
   <si>
@@ -57,13 +54,265 @@
     <t>085274817886</t>
   </si>
   <si>
-    <t>LARUANG AC</t>
-  </si>
-  <si>
     <t>PAYAKUMBUH</t>
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>PT. Philip Batam</t>
+  </si>
+  <si>
+    <t>Laruang AC</t>
+  </si>
+  <si>
+    <t>PT. Cipta Mandiri Teknik ULP Padang Panjang</t>
+  </si>
+  <si>
+    <t>PT. Cipta Mandiri Teknik ULP Baso</t>
+  </si>
+  <si>
+    <t>PT. PLN ULP Baso</t>
+  </si>
+  <si>
+    <t>PT. Tarusan Rimki Pratama</t>
+  </si>
+  <si>
+    <t>PT. Lucky Jaya Teknik</t>
+  </si>
+  <si>
+    <t>PT. Satria Teknik Mandiri</t>
+  </si>
+  <si>
+    <t>PT. Cipta Mandiri Teknik ULP Bukittinggi</t>
+  </si>
+  <si>
+    <t>Atiyan Hotel</t>
+  </si>
+  <si>
+    <t>Monopoli Hotel</t>
+  </si>
+  <si>
+    <t>PT. PLN UP3 Bukittinggi</t>
+  </si>
+  <si>
+    <t>DA'I DINAMO</t>
+  </si>
+  <si>
+    <t>Cooler Service</t>
+  </si>
+  <si>
+    <t>Hotel Grand Malindo</t>
+  </si>
+  <si>
+    <t>MJ ELEKTRONIK</t>
+  </si>
+  <si>
+    <t>CV. ANSERI GROUP KOTO</t>
+  </si>
+  <si>
+    <t>UP Listrik SMK BKT</t>
+  </si>
+  <si>
+    <t>PT. Karya Bakti Mulia</t>
+  </si>
+  <si>
+    <t>PT. SIGMA Teknindo Padang</t>
+  </si>
+  <si>
+    <t>CV.SARANTAU WIJAYA</t>
+  </si>
+  <si>
+    <t>HAN'S AC</t>
+  </si>
+  <si>
+    <t>SEKAWAN AC</t>
+  </si>
+  <si>
+    <t>RUMAH AC</t>
+  </si>
+  <si>
+    <t>PT. ELANG CONSUS JAYA</t>
+  </si>
+  <si>
+    <t>PT. Haliyora Padang</t>
+  </si>
+  <si>
+    <t>PT Kurnia Abadi Padang</t>
+  </si>
+  <si>
+    <t>PT. Putra Caniago Group</t>
+  </si>
+  <si>
+    <t>PT. Basko Grand Hotel</t>
+  </si>
+  <si>
+    <t>Mercure Padang</t>
+  </si>
+  <si>
+    <t>CV. Pancoran Karya</t>
+  </si>
+  <si>
+    <t>Berkah Jaya AC</t>
+  </si>
+  <si>
+    <t>PT. LG ELEKTRONIK INDONESIA</t>
+  </si>
+  <si>
+    <t>PT. Karya Teknik Airconditioning</t>
+  </si>
+  <si>
+    <t>Panasonic Service Center</t>
+  </si>
+  <si>
+    <t>Maju Teknik</t>
+  </si>
+  <si>
+    <t>Indoteknik Jaya Mandiri</t>
+  </si>
+  <si>
+    <t>Alifa Elektronik</t>
+  </si>
+  <si>
+    <t>MICROEGA TEKNIK AC</t>
+  </si>
+  <si>
+    <t>CV. Mitra Jasindo</t>
+  </si>
+  <si>
+    <t>ULP. Simpang Tiga</t>
+  </si>
+  <si>
+    <t>PT. PLN UP3 Pekan Baru</t>
+  </si>
+  <si>
+    <t>CV . Termo Jaya Mandiri</t>
+  </si>
+  <si>
+    <t>Royal Denai Hotel</t>
+  </si>
+  <si>
+    <t>The valmount hotel</t>
+  </si>
+  <si>
+    <t>PT. PLN UP3 Bukittinggi ULP Koto Tuo</t>
+  </si>
+  <si>
+    <t>PT. Jayaguna Teknik Perkasa</t>
+  </si>
+  <si>
+    <t>PT. Mitra Unggul Pusaka</t>
+  </si>
+  <si>
+    <t>PT. RIAU Muda Jasasarana</t>
+  </si>
+  <si>
+    <t>ACM</t>
+  </si>
+  <si>
+    <t>Kawasan Industri Batamindo</t>
+  </si>
+  <si>
+    <t>Jln.Soekarno Hatta no.243 (depan SPBU Koto nan empat) kel.Bulakan balai kandi Payakumbuh, Bulakan Balai Kandih, Kec. Payakumbuh Kota Payakumbuh, Sumatera Barat, 26223</t>
+  </si>
+  <si>
+    <t>Jl. Tanjuang Alam – Batu Taba</t>
+  </si>
+  <si>
+    <t>Jln. Raya Bukittinggi - Payakumbuh Koto Hilalang</t>
+  </si>
+  <si>
+    <t>PKL008</t>
+  </si>
+  <si>
+    <t>Jl. Soekarno Hatta, Pulai Anak Air</t>
+  </si>
+  <si>
+    <t>Jl. Laras Datuk Bandaro, Bukit Cangang Kayu Ramang</t>
+  </si>
+  <si>
+    <t>Jl. By Pass, Aur Kuning</t>
+  </si>
+  <si>
+    <t>Jl. Sudirman No. 1</t>
+  </si>
+  <si>
+    <t>Jl. Panorama No. 30</t>
+  </si>
+  <si>
+    <t>Jl. Raya Taluak 127B Jambu Air</t>
+  </si>
+  <si>
+    <t>Jl. Koto Baru IV No. 29</t>
+  </si>
+  <si>
+    <t>Jl. Kp. Nias II No. 51</t>
+  </si>
+  <si>
+    <t>Jl. Kp. Kalawi No.41, Lubuk Lintah, Kec. Kuranji, Kota Padang, Sumatera Barat 25175</t>
+  </si>
+  <si>
+    <t>Jl. Dr. sutomo dalam No.31, Simpang Haru, Kec. Padang Timur</t>
+  </si>
+  <si>
+    <t>Jl. Raya Ampang No.5, Ampang, Kec. Kuranji, Kota Padang, Sumatera Barat 25171</t>
+  </si>
+  <si>
+    <t>Jl. Garuda No.10, Dadok Tunggul Hitam, Kec. Koto Tangah, Kota Padang, Sumatera Barat 25586</t>
+  </si>
+  <si>
+    <t>Jl. Purus IV GG IV No. 5</t>
+  </si>
+  <si>
+    <t>Jln. Diponegoro No 11 Padang</t>
+  </si>
+  <si>
+    <t>Batipuh Panjang, Koto Tangah, Padang City</t>
+  </si>
+  <si>
+    <t>JALAN PARAK KARAKAH NO.16 PADANG</t>
+  </si>
+  <si>
+    <t>Jl. Prof. Dr. Hamka No.2A, Air Tawar</t>
+  </si>
+  <si>
+    <t>Jl Purus IV No 8 Padang, West Sumatra Indonesia</t>
+  </si>
+  <si>
+    <t>Jln. Riau 2D – 2 E P. Baru</t>
+  </si>
+  <si>
+    <t>Jl. Rambutan No 11B Marpoyan Damai</t>
+  </si>
+  <si>
+    <t>Jln. Kaharudin Nasution No. 11</t>
+  </si>
+  <si>
+    <t>Jl. Pemudi Gg. Karya, Tampan</t>
+  </si>
+  <si>
+    <t>Jl. Katio No.17, Tengkerang Tengah</t>
+  </si>
+  <si>
+    <t>Jln. Paus Ujung Q6 Tangkerang Barat - Pekan Baru</t>
+  </si>
+  <si>
+    <t>Jl. Dr. Setia Budhi No.57, Rintis, Kec. Lima Puluh, Kota Pekanbaru</t>
+  </si>
+  <si>
+    <t>jln arengka no.007 sebelah indogrosir - kota pekanbaru</t>
+  </si>
+  <si>
+    <t>Jl. Dr. Abdul Rivai No.26, Benteng Ps. Atas, Kec. Guguk Panjang, Kota Bukittinggi, Sumatera Barat 26136</t>
+  </si>
+  <si>
+    <t>Tarok Dipo, Kec. Guguk Panjang, Kota Bukittinggi, Sumatera Barat 26138</t>
+  </si>
+  <si>
+    <t>Ruko, Jl. Bengkong Sadai No.1 Blok AA, Sadai, Kec. Bengkong, Kota Batam, Kepulauan Riau 29432</t>
+  </si>
+  <si>
+    <t>Segati, Kec, Langgam, Kab, Pelalawan, Riau 28381</t>
   </si>
 </sst>
 </file>
@@ -416,12 +665,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E923898F-7C6A-45BD-A64C-F288427B5F1A}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="40.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.42578125" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" customWidth="1"/>
     <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
@@ -429,7 +678,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -455,19 +704,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -478,10 +727,685 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12">
         <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>48</v>
+      </c>
+      <c r="C39" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>49</v>
+      </c>
+      <c r="C40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>60</v>
+      </c>
+      <c r="C51" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
